--- a/research/traditional_assets/database/data/new_zealand/new_zealand_drugs_biotechnology.xlsx
+++ b/research/traditional_assets/database/data/new_zealand/new_zealand_drugs_biotechnology.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0895</v>
+        <v>0.428</v>
       </c>
       <c r="G2">
-        <v>-0.1232550221314267</v>
+        <v>-0.09181011997913405</v>
       </c>
       <c r="H2">
-        <v>-0.5502213142662581</v>
+        <v>-0.4608763693270735</v>
       </c>
       <c r="I2">
-        <v>-0.6321637371881044</v>
+        <v>-0.4488784559207094</v>
       </c>
       <c r="J2">
-        <v>-0.6321637371881044</v>
+        <v>-0.4488784559207094</v>
       </c>
       <c r="K2">
-        <v>-18.57</v>
+        <v>-13.069</v>
       </c>
       <c r="L2">
-        <v>-0.6322778345250256</v>
+        <v>-0.3408711528429837</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>86.7</v>
+        <v>28.29</v>
       </c>
       <c r="V2">
-        <v>0.0875050464271296</v>
+        <v>0.05563421828908555</v>
       </c>
       <c r="W2">
-        <v>-0.3667747427908998</v>
+        <v>-0.1004868191801997</v>
       </c>
       <c r="X2">
-        <v>0.05943847931077153</v>
+        <v>0.1134562206890284</v>
       </c>
       <c r="Y2">
-        <v>-0.4262132221016713</v>
+        <v>-0.2139430398692281</v>
       </c>
       <c r="Z2">
-        <v>0.5015090966570601</v>
+        <v>0.701555352241537</v>
       </c>
       <c r="AA2">
-        <v>-0.4037651803733191</v>
+        <v>-0.7009703513364313</v>
       </c>
       <c r="AB2">
-        <v>0.05904577719902355</v>
+        <v>0.1128413625815647</v>
       </c>
       <c r="AC2">
-        <v>-0.4628109575723426</v>
+        <v>-0.813811713917996</v>
       </c>
       <c r="AD2">
-        <v>5.850000000000001</v>
+        <v>4.25</v>
       </c>
       <c r="AE2">
-        <v>0.01324480607311933</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>5.86324480607312</v>
+        <v>4.25</v>
       </c>
       <c r="AG2">
-        <v>-80.83675519392688</v>
+        <v>-24.04</v>
       </c>
       <c r="AH2">
-        <v>0.005882874518176867</v>
+        <v>0.008288639687957094</v>
       </c>
       <c r="AI2">
-        <v>0.04147644470184961</v>
+        <v>0.03600169419737399</v>
       </c>
       <c r="AJ2">
-        <v>-0.08883518719610967</v>
+        <v>-0.04962225983569335</v>
       </c>
       <c r="AK2">
-        <v>-1.478813697955703</v>
+        <v>-0.267825311942959</v>
       </c>
       <c r="AL2">
-        <v>1.2</v>
+        <v>0.215</v>
       </c>
       <c r="AM2">
-        <v>0.858</v>
+        <v>-1.125</v>
       </c>
       <c r="AN2">
-        <v>-0.3473046782236998</v>
+        <v>-0.2740167633784655</v>
       </c>
       <c r="AO2">
-        <v>-15.475</v>
+        <v>-80.04651162790698</v>
       </c>
       <c r="AP2">
-        <v>4.799142436115345</v>
+        <v>1.54996776273372</v>
       </c>
       <c r="AQ2">
-        <v>-21.64335664335664</v>
+        <v>15.29777777777778</v>
       </c>
     </row>
     <row r="3">
@@ -716,22 +716,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>-0.01588785046728975</v>
+        <v>0.08310344827586208</v>
       </c>
       <c r="H3">
-        <v>-0.2504672897196262</v>
+        <v>-0.126551724137931</v>
       </c>
       <c r="I3">
-        <v>-0.2975069608044217</v>
+        <v>-0.09344827586206897</v>
       </c>
       <c r="J3">
-        <v>-0.2975069608044217</v>
+        <v>-0.09344827586206897</v>
       </c>
       <c r="K3">
-        <v>-7.47</v>
+        <v>-0.969</v>
       </c>
       <c r="L3">
-        <v>-0.3490654205607477</v>
+        <v>-0.03341379310344827</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -755,73 +755,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>31.3</v>
+        <v>6.79</v>
       </c>
       <c r="V3">
-        <v>0.1232768806616778</v>
+        <v>0.02697655939610648</v>
       </c>
       <c r="W3">
-        <v>-0.1813106796116505</v>
+        <v>-0.01366713681241185</v>
       </c>
       <c r="X3">
-        <v>0.05966858105423655</v>
+        <v>0.1136782217984552</v>
       </c>
       <c r="Y3">
-        <v>-0.240979260665887</v>
+        <v>-0.127345358610867</v>
       </c>
       <c r="Z3">
-        <v>0.5388630444200676</v>
+        <v>0.6616472735569243</v>
       </c>
       <c r="AA3">
-        <v>-0.1603155066352324</v>
+        <v>-0.06182979694273327</v>
       </c>
       <c r="AB3">
-        <v>0.05896407747001609</v>
+        <v>0.1127597285830306</v>
       </c>
       <c r="AC3">
-        <v>-0.2192795841052485</v>
+        <v>-0.1745895255257638</v>
       </c>
       <c r="AD3">
-        <v>4.23</v>
+        <v>3.16</v>
       </c>
       <c r="AE3">
-        <v>0.01324480607311933</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>4.24324480607312</v>
+        <v>3.16</v>
       </c>
       <c r="AG3">
-        <v>-27.05675519392688</v>
+        <v>-3.63</v>
       </c>
       <c r="AH3">
-        <v>0.01643755895786002</v>
+        <v>0.01239896413717335</v>
       </c>
       <c r="AI3">
-        <v>0.05646874602000389</v>
+        <v>0.05183727034120736</v>
       </c>
       <c r="AJ3">
-        <v>-0.1192751197729407</v>
+        <v>-0.01463296650139074</v>
       </c>
       <c r="AK3">
-        <v>-0.617124834478013</v>
+        <v>-0.06701126084548643</v>
       </c>
       <c r="AL3">
-        <v>1.2</v>
+        <v>0.215</v>
       </c>
       <c r="AM3">
-        <v>1.056</v>
+        <v>-0.252</v>
       </c>
       <c r="AN3">
-        <v>-0.8916526138279934</v>
+        <v>-2.611570247933884</v>
       </c>
       <c r="AO3">
-        <v>-5.308333333333334</v>
+        <v>-12.6046511627907</v>
       </c>
       <c r="AP3">
-        <v>5.703363236493862</v>
+        <v>3</v>
       </c>
       <c r="AQ3">
-        <v>-6.03219696969697</v>
+        <v>10.75396825396825</v>
       </c>
     </row>
     <row r="4">
@@ -841,25 +841,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0895</v>
+        <v>0.428</v>
       </c>
       <c r="G4">
-        <v>-0.4115432873274782</v>
+        <v>-0.6349036402569593</v>
       </c>
       <c r="H4">
-        <v>-1.355081555834379</v>
+        <v>-1.498929336188437</v>
       </c>
       <c r="I4">
-        <v>-1.530740276035132</v>
+        <v>-1.552462526766595</v>
       </c>
       <c r="J4">
-        <v>-1.530740276035132</v>
+        <v>-1.552462526766595</v>
       </c>
       <c r="K4">
-        <v>-11.1</v>
+        <v>-12.1</v>
       </c>
       <c r="L4">
-        <v>-1.392722710163112</v>
+        <v>-1.295503211991435</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -883,70 +883,70 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>55.4</v>
+        <v>21.5</v>
       </c>
       <c r="V4">
-        <v>0.07517980730085494</v>
+        <v>0.0837227414330218</v>
       </c>
       <c r="W4">
-        <v>-0.5522388059701492</v>
+        <v>-0.1873065015479876</v>
       </c>
       <c r="X4">
-        <v>0.05920837756730651</v>
+        <v>0.1132342195796016</v>
       </c>
       <c r="Y4">
-        <v>-0.6114471835374556</v>
+        <v>-0.3005407211275892</v>
       </c>
       <c r="Z4">
-        <v>0.4228116710875331</v>
+        <v>0.8632162661737522</v>
       </c>
       <c r="AA4">
-        <v>-0.6472148541114058</v>
+        <v>-1.340110905730129</v>
       </c>
       <c r="AB4">
-        <v>0.05912747692803101</v>
+        <v>0.1129229965800989</v>
       </c>
       <c r="AC4">
-        <v>-0.7063423310394368</v>
+        <v>-1.453033902310228</v>
       </c>
       <c r="AD4">
-        <v>1.62</v>
+        <v>1.09</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.62</v>
+        <v>1.09</v>
       </c>
       <c r="AG4">
-        <v>-53.78</v>
+        <v>-20.41</v>
       </c>
       <c r="AH4">
-        <v>0.002193576341872935</v>
+        <v>0.004226608243824887</v>
       </c>
       <c r="AI4">
-        <v>0.02446390818483842</v>
+        <v>0.01909266071115782</v>
       </c>
       <c r="AJ4">
-        <v>-0.07872701721513058</v>
+        <v>-0.08634036972799188</v>
       </c>
       <c r="AK4">
-        <v>-4.970425138632166</v>
+        <v>-0.5734756954200617</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-0.198</v>
+        <v>-0.873</v>
       </c>
       <c r="AN4">
-        <v>-0.1338842975206612</v>
+        <v>-0.07622377622377623</v>
       </c>
       <c r="AP4">
-        <v>4.444628099173554</v>
+        <v>1.427272727272727</v>
       </c>
       <c r="AQ4">
-        <v>61.61616161616161</v>
+        <v>16.60939289805269</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/new_zealand/new_zealand_drugs_biotechnology.xlsx
+++ b/research/traditional_assets/database/data/new_zealand/new_zealand_drugs_biotechnology.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.428</v>
+        <v>0.377</v>
       </c>
       <c r="G2">
-        <v>-0.09181011997913405</v>
+        <v>-0.01663023679417121</v>
       </c>
       <c r="H2">
-        <v>-0.4608763693270735</v>
+        <v>-0.359799635701275</v>
       </c>
       <c r="I2">
-        <v>-0.4488784559207094</v>
+        <v>-0.4695810564663023</v>
       </c>
       <c r="J2">
-        <v>-0.4488784559207094</v>
+        <v>-0.4695810564663023</v>
       </c>
       <c r="K2">
-        <v>-13.069</v>
+        <v>-23.98</v>
       </c>
       <c r="L2">
-        <v>-0.3408711528429837</v>
+        <v>-0.4367941712204007</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>28.29</v>
+        <v>14.68</v>
       </c>
       <c r="V2">
-        <v>0.05563421828908555</v>
+        <v>0.05770440251572326</v>
       </c>
       <c r="W2">
-        <v>-0.1004868191801997</v>
+        <v>-0.2127224419179436</v>
       </c>
       <c r="X2">
-        <v>0.1134562206890284</v>
+        <v>0.09232433670462184</v>
       </c>
       <c r="Y2">
-        <v>-0.2139430398692281</v>
+        <v>-0.3050467786225655</v>
       </c>
       <c r="Z2">
-        <v>0.701555352241537</v>
+        <v>0.6116310160427809</v>
       </c>
       <c r="AA2">
-        <v>-0.7009703513364313</v>
+        <v>-0.3401107924990078</v>
       </c>
       <c r="AB2">
-        <v>0.1128413625815647</v>
+        <v>0.09148584323122555</v>
       </c>
       <c r="AC2">
-        <v>-0.813811713917996</v>
+        <v>-0.4315966357302334</v>
       </c>
       <c r="AD2">
-        <v>4.25</v>
+        <v>4.909999999999999</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>4.25</v>
+        <v>4.909999999999999</v>
       </c>
       <c r="AG2">
-        <v>-24.04</v>
+        <v>-9.77</v>
       </c>
       <c r="AH2">
-        <v>0.008288639687957094</v>
+        <v>0.01893486560487447</v>
       </c>
       <c r="AI2">
-        <v>0.03600169419737399</v>
+        <v>0.04702614692079302</v>
       </c>
       <c r="AJ2">
-        <v>-0.04962225983569335</v>
+        <v>-0.0399378653476679</v>
       </c>
       <c r="AK2">
-        <v>-0.267825311942959</v>
+        <v>-0.1088822021620417</v>
       </c>
       <c r="AL2">
-        <v>0.215</v>
+        <v>0.256</v>
       </c>
       <c r="AM2">
-        <v>-1.125</v>
+        <v>-2.954</v>
       </c>
       <c r="AN2">
-        <v>-0.2740167633784655</v>
+        <v>-0.2104586369481354</v>
       </c>
       <c r="AO2">
-        <v>-80.04651162790698</v>
+        <v>-100.703125</v>
       </c>
       <c r="AP2">
-        <v>1.54996776273372</v>
+        <v>0.4187741105872267</v>
       </c>
       <c r="AQ2">
-        <v>15.29777777777778</v>
+        <v>8.727149627623563</v>
       </c>
     </row>
     <row r="3">
@@ -716,22 +716,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.08310344827586208</v>
+        <v>0.1461363636363636</v>
       </c>
       <c r="H3">
-        <v>-0.126551724137931</v>
+        <v>-0.001338383838383838</v>
       </c>
       <c r="I3">
-        <v>-0.09344827586206897</v>
+        <v>-0.1156565656565657</v>
       </c>
       <c r="J3">
-        <v>-0.09344827586206897</v>
+        <v>-0.1156565656565657</v>
       </c>
       <c r="K3">
-        <v>-0.969</v>
+        <v>-4.98</v>
       </c>
       <c r="L3">
-        <v>-0.03341379310344827</v>
+        <v>-0.1257575757575758</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -755,73 +755,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>6.79</v>
+        <v>2.38</v>
       </c>
       <c r="V3">
-        <v>0.02697655939610648</v>
+        <v>0.01224909933093155</v>
       </c>
       <c r="W3">
-        <v>-0.01366713681241185</v>
+        <v>-0.08615916955017303</v>
       </c>
       <c r="X3">
-        <v>0.1136782217984552</v>
+        <v>0.09245282685641207</v>
       </c>
       <c r="Y3">
-        <v>-0.127345358610867</v>
+        <v>-0.1786119964065851</v>
       </c>
       <c r="Z3">
-        <v>0.6616472735569243</v>
+        <v>0.7310319364962157</v>
       </c>
       <c r="AA3">
-        <v>-0.06182979694273327</v>
+        <v>-0.08454864316042091</v>
       </c>
       <c r="AB3">
-        <v>0.1127597285830306</v>
+        <v>0.09130995964005276</v>
       </c>
       <c r="AC3">
-        <v>-0.1745895255257638</v>
+        <v>-0.1758586028004737</v>
       </c>
       <c r="AD3">
-        <v>3.16</v>
+        <v>4.06</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3.16</v>
+        <v>4.06</v>
       </c>
       <c r="AG3">
-        <v>-3.63</v>
+        <v>1.68</v>
       </c>
       <c r="AH3">
-        <v>0.01239896413717335</v>
+        <v>0.02046783625730994</v>
       </c>
       <c r="AI3">
-        <v>0.05183727034120736</v>
+        <v>0.06500160102465577</v>
       </c>
       <c r="AJ3">
-        <v>-0.01463296650139074</v>
+        <v>0.008572303296254717</v>
       </c>
       <c r="AK3">
-        <v>-0.06701126084548643</v>
+        <v>0.02796271637816245</v>
       </c>
       <c r="AL3">
-        <v>0.215</v>
+        <v>0.256</v>
       </c>
       <c r="AM3">
-        <v>-0.252</v>
+        <v>-0.8140000000000001</v>
       </c>
       <c r="AN3">
-        <v>-2.611570247933884</v>
+        <v>-1.543726235741445</v>
       </c>
       <c r="AO3">
-        <v>-12.6046511627907</v>
+        <v>-17.890625</v>
       </c>
       <c r="AP3">
-        <v>3</v>
+        <v>-0.6387832699619771</v>
       </c>
       <c r="AQ3">
-        <v>10.75396825396825</v>
+        <v>5.626535626535627</v>
       </c>
     </row>
     <row r="4">
@@ -841,25 +841,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.428</v>
+        <v>0.377</v>
       </c>
       <c r="G4">
-        <v>-0.6349036402569593</v>
+        <v>-0.4379084967320261</v>
       </c>
       <c r="H4">
-        <v>-1.498929336188437</v>
+        <v>-1.287581699346405</v>
       </c>
       <c r="I4">
-        <v>-1.552462526766595</v>
+        <v>-1.38562091503268</v>
       </c>
       <c r="J4">
-        <v>-1.552462526766595</v>
+        <v>-1.38562091503268</v>
       </c>
       <c r="K4">
-        <v>-12.1</v>
+        <v>-19</v>
       </c>
       <c r="L4">
-        <v>-1.295503211991435</v>
+        <v>-1.241830065359477</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -883,70 +883,70 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>21.5</v>
+        <v>12.3</v>
       </c>
       <c r="V4">
-        <v>0.0837227414330218</v>
+        <v>0.2046589018302829</v>
       </c>
       <c r="W4">
-        <v>-0.1873065015479876</v>
+        <v>-0.3392857142857143</v>
       </c>
       <c r="X4">
-        <v>0.1132342195796016</v>
+        <v>0.0921958465528316</v>
       </c>
       <c r="Y4">
-        <v>-0.3005407211275892</v>
+        <v>-0.4314815608385459</v>
       </c>
       <c r="Z4">
-        <v>0.8632162661737522</v>
+        <v>0.4298960382129812</v>
       </c>
       <c r="AA4">
-        <v>-1.340110905730129</v>
+        <v>-0.5956729418375948</v>
       </c>
       <c r="AB4">
-        <v>0.1129229965800989</v>
+        <v>0.09166172682239834</v>
       </c>
       <c r="AC4">
-        <v>-1.453033902310228</v>
+        <v>-0.6873346686599932</v>
       </c>
       <c r="AD4">
-        <v>1.09</v>
+        <v>0.85</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.09</v>
+        <v>0.85</v>
       </c>
       <c r="AG4">
-        <v>-20.41</v>
+        <v>-11.45</v>
       </c>
       <c r="AH4">
-        <v>0.004226608243824887</v>
+        <v>0.01394585726004922</v>
       </c>
       <c r="AI4">
-        <v>0.01909266071115782</v>
+        <v>0.02026221692491061</v>
       </c>
       <c r="AJ4">
-        <v>-0.08634036972799188</v>
+        <v>-0.2353545734840699</v>
       </c>
       <c r="AK4">
-        <v>-0.5734756954200617</v>
+        <v>-0.3861720067453626</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-0.873</v>
+        <v>-2.14</v>
       </c>
       <c r="AN4">
-        <v>-0.07622377622377623</v>
+        <v>-0.04106280193236715</v>
       </c>
       <c r="AP4">
-        <v>1.427272727272727</v>
+        <v>0.5531400966183576</v>
       </c>
       <c r="AQ4">
-        <v>16.60939289805269</v>
+        <v>9.906542056074766</v>
       </c>
     </row>
   </sheetData>
